--- a/reports/Brazil_1.1_trade_balance_2003-2025.xlsx
+++ b/reports/Brazil_1.1_trade_balance_2003-2025.xlsx
@@ -558,10 +558,10 @@
         <v>129101368389.674</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>1.076891065978263</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>0.8991108680570035</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -599,10 +599,10 @@
         <v>167388762647.364</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>1.12036478553807</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>0.8874605071601662</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -640,10 +640,10 @@
         <v>201288213228.965</v>
       </c>
       <c r="L4">
-        <v>1</v>
+        <v>1.085246150989171</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>0.9209750198837761</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -681,10 +681,10 @@
         <v>238959254049.492</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>1.056163997893406</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>0.935336455595039</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -722,10 +722,10 @@
         <v>295184048798.532</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>1.070055745376552</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>0.9108372729229168</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -763,10 +763,10 @@
         <v>392345822072.257</v>
       </c>
       <c r="L7">
-        <v>1</v>
+        <v>1.074739954278584</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>0.8849501790416698</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -804,10 +804,10 @@
         <v>295113199720.938</v>
       </c>
       <c r="L8">
-        <v>1</v>
+        <v>1.067633780259104</v>
       </c>
       <c r="M8">
-        <v>1</v>
+        <v>0.9018487994954367</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -845,10 +845,10 @@
         <v>398955842905.979</v>
       </c>
       <c r="L9">
-        <v>1</v>
+        <v>1.055200230896452</v>
       </c>
       <c r="M9">
-        <v>1</v>
+        <v>0.928461329889104</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -886,10 +886,10 @@
         <v>502087354506.017</v>
       </c>
       <c r="L10">
-        <v>1</v>
+        <v>1.048012007626555</v>
       </c>
       <c r="M10">
-        <v>1</v>
+        <v>0.9247166413921785</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -927,10 +927,10 @@
         <v>493397515490.859</v>
       </c>
       <c r="L11">
-        <v>1</v>
+        <v>1.024878016918935</v>
       </c>
       <c r="M11">
-        <v>1</v>
+        <v>0.909920046961714</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -968,10 +968,10 @@
         <v>478588061692.993</v>
       </c>
       <c r="L12">
-        <v>1</v>
+        <v>1.096272107927676</v>
       </c>
       <c r="M12">
-        <v>1</v>
+        <v>0.935935664538484</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1009,10 +1009,10 @@
         <v>454600704178.041</v>
       </c>
       <c r="L13">
-        <v>1</v>
+        <v>1.099731807881065</v>
       </c>
       <c r="M13">
-        <v>1</v>
+        <v>0.9374095870834864</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1050,10 +1050,10 @@
         <v>366974430543.595</v>
       </c>
       <c r="L14">
-        <v>1</v>
+        <v>1.127917777771812</v>
       </c>
       <c r="M14">
-        <v>1</v>
+        <v>0.9023694071658215</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1091,10 +1091,10 @@
         <v>341113648853.062</v>
       </c>
       <c r="L15">
-        <v>1</v>
+        <v>1.040578287528994</v>
       </c>
       <c r="M15">
-        <v>1</v>
+        <v>0.8908165732408023</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1132,10 +1132,10 @@
         <v>398995710997.916</v>
       </c>
       <c r="L16">
-        <v>1</v>
+        <v>1.019875153707721</v>
       </c>
       <c r="M16">
-        <v>1</v>
+        <v>0.9095304348098556</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1173,10 +1173,10 @@
         <v>436163257324.89</v>
       </c>
       <c r="L17">
-        <v>1</v>
+        <v>1.082349874377008</v>
       </c>
       <c r="M17">
-        <v>1</v>
+        <v>0.8988131359594541</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -1214,10 +1214,10 @@
         <v>425966953065.582</v>
       </c>
       <c r="L18">
-        <v>1</v>
+        <v>1.077051119289651</v>
       </c>
       <c r="M18">
-        <v>1</v>
+        <v>0.8966167269057576</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -1255,10 +1255,10 @@
         <v>394443195905.47</v>
       </c>
       <c r="L19">
-        <v>1</v>
+        <v>1.060820666224684</v>
       </c>
       <c r="M19">
-        <v>1</v>
+        <v>0.8802265589495127</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -1296,10 +1296,10 @@
         <v>536234598119.728</v>
       </c>
       <c r="L20">
-        <v>1</v>
+        <v>1.066295543489126</v>
       </c>
       <c r="M20">
-        <v>1</v>
+        <v>0.8882721907346954</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -1337,10 +1337,10 @@
         <v>615555488002.488</v>
       </c>
       <c r="L21">
-        <v>1</v>
+        <v>1.184882000539245</v>
       </c>
       <c r="M21">
-        <v>1</v>
+        <v>0.9068282927502981</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -1378,10 +1378,10 @@
         <v>599197906707.338</v>
       </c>
       <c r="L22">
-        <v>1</v>
+        <v>1.121203936034552</v>
       </c>
       <c r="M22">
-        <v>1</v>
+        <v>0.908749194814978</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -1419,10 +1419,10 @@
         <v>603406958026.818</v>
       </c>
       <c r="L23">
-        <v>1</v>
+        <v>1.121892508159977</v>
       </c>
       <c r="M23">
-        <v>1</v>
+        <v>0.9466960303832054</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -1460,10 +1460,10 @@
         <v>51274347233.867</v>
       </c>
       <c r="L24">
-        <v>1</v>
+        <v>17.20709628959792</v>
       </c>
       <c r="M24">
-        <v>1</v>
+        <v>10.19667582759915</v>
       </c>
     </row>
   </sheetData>
